--- a/E/MED01S.xlsx
+++ b/E/MED01S.xlsx
@@ -310,79 +310,79 @@
     <t>PT,(E-2B)</t>
   </si>
   <si>
-    <t>10030787</t>
-  </si>
-  <si>
-    <t>ACTF PILEK&amp;BT.DHK 60</t>
+    <t>20143398</t>
+  </si>
+  <si>
+    <t>ACTF SYRUP PILEK 25</t>
+  </si>
+  <si>
+    <t>20138372</t>
+  </si>
+  <si>
+    <t>KOMIX OBH 6X7ML</t>
+  </si>
+  <si>
+    <t>20092712</t>
+  </si>
+  <si>
+    <t>KOMIX HERBAL 4X15ML</t>
+  </si>
+  <si>
+    <t>10008599</t>
+  </si>
+  <si>
+    <t>OBH/C ANAK STRW 60ML</t>
+  </si>
+  <si>
+    <t>10023206</t>
+  </si>
+  <si>
+    <t>TERMOREX PLUS 60 ML</t>
+  </si>
+  <si>
+    <t>10006565</t>
+  </si>
+  <si>
+    <t>TEMPRA T/PNS ANGR 60</t>
+  </si>
+  <si>
+    <t>10000548</t>
+  </si>
+  <si>
+    <t>CAP LANG NORIT (40)</t>
+  </si>
+  <si>
+    <t>10038823</t>
+  </si>
+  <si>
+    <t>COMBANTRIN JRK 10ML</t>
+  </si>
+  <si>
+    <t>20021454</t>
+  </si>
+  <si>
+    <t>MYLANTA MAAG MINT 50</t>
+  </si>
+  <si>
+    <t>20052643</t>
+  </si>
+  <si>
+    <t>PROMAG HRBAL BOX 6'S</t>
+  </si>
+  <si>
+    <t>20057840</t>
+  </si>
+  <si>
+    <t>POLYSILANE BTL 100</t>
+  </si>
+  <si>
+    <t>20021214</t>
+  </si>
+  <si>
+    <t>VGTA HERBAL ANGR 6'S</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138372</t>
-  </si>
-  <si>
-    <t>KOMIX OBH 6X7ML</t>
-  </si>
-  <si>
-    <t>20092712</t>
-  </si>
-  <si>
-    <t>KOMIX HERBAL 4X15ML</t>
-  </si>
-  <si>
-    <t>10008599</t>
-  </si>
-  <si>
-    <t>OBH/C ANAK STRW 60ML</t>
-  </si>
-  <si>
-    <t>10023206</t>
-  </si>
-  <si>
-    <t>TERMOREX PLUS 60 ML</t>
-  </si>
-  <si>
-    <t>10006565</t>
-  </si>
-  <si>
-    <t>TEMPRA T/PNS ANGR 60</t>
-  </si>
-  <si>
-    <t>10000548</t>
-  </si>
-  <si>
-    <t>CAP LANG NORIT (40)</t>
-  </si>
-  <si>
-    <t>10038823</t>
-  </si>
-  <si>
-    <t>COMBANTRIN JRK 10ML</t>
-  </si>
-  <si>
-    <t>20021454</t>
-  </si>
-  <si>
-    <t>MYLANTA MAAG MINT 50</t>
-  </si>
-  <si>
-    <t>20052643</t>
-  </si>
-  <si>
-    <t>PROMAG HRBAL BOX 6'S</t>
-  </si>
-  <si>
-    <t>20057840</t>
-  </si>
-  <si>
-    <t>POLYSILANE BTL 100</t>
-  </si>
-  <si>
-    <t>20021214</t>
-  </si>
-  <si>
-    <t>VGTA HERBAL ANGR 6'S</t>
   </si>
   <si>
     <t>20107145</t>
@@ -2360,15 +2360,15 @@
         <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2405,10 +2405,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         <v>46</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2960,7 +2960,7 @@
         <v>46</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,7 +3300,7 @@
         <v>46</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,7 +3320,7 @@
         <v>49</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,7 +3340,7 @@
         <v>53</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3500,7 +3500,7 @@
         <v>221</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3780,7 +3780,7 @@
         <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3840,7 +3840,7 @@
         <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3880,7 +3880,7 @@
         <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4640,7 +4640,7 @@
         <v>46</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4720,7 +4720,7 @@
         <v>53</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">

--- a/E/MED01S.xlsx
+++ b/E/MED01S.xlsx
@@ -76,13 +76,22 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>20139960</t>
+  </si>
+  <si>
+    <t>EJ SPORT ORANGE 2S</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>10037376</t>
   </si>
   <si>
     <t>NATUR-E VIT ALMH 16</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>20073420</t>
@@ -91,7 +100,7 @@
     <t>NATUR-E 300 DN 16'S</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>20061582</t>
@@ -100,7 +109,7 @@
     <t>MADU TJ JYBEE JRK100</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>RT,(E-5B)</t>
@@ -112,7 +121,7 @@
     <t>CURCUMA GROW ORGE100</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>20137504</t>
@@ -121,7 +130,7 @@
     <t>SKTNK/ABC C.MADU 24S</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>10006069</t>
@@ -130,7 +139,7 @@
     <t>SAKATONIK STR 30X800</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>10016755</t>
@@ -139,7 +148,7 @@
     <t>GELIGA BALSAM OTOT20</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>RT,(E-6B)</t>
@@ -151,7 +160,7 @@
     <t>KALPANAX K CREAM 5GR</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>20094802</t>
@@ -160,7 +169,7 @@
     <t>88 KRIM ANTI JAMUR 5</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>RT,(E-7B)</t>
@@ -172,7 +181,7 @@
     <t>COUNTERPAIN CREAM 30</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>20047965</t>
@@ -181,7 +190,7 @@
     <t>HOT IN CREAM 120ML</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>20057841</t>
@@ -190,7 +199,7 @@
     <t>HOT IN CREAM 60G</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>20080244</t>
@@ -199,7 +208,448 @@
     <t>HOT IN CRM STRNG 120</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20054951</t>
+  </si>
+  <si>
+    <t>S/M TOLAK/A ANAK 5'S</t>
+  </si>
+  <si>
+    <t>20034577</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN+MDU 5'S</t>
+  </si>
+  <si>
+    <t>20122907</t>
+  </si>
+  <si>
+    <t>S/M TLK.ANGN FLU 5'S</t>
+  </si>
+  <si>
+    <t>20064502</t>
+  </si>
+  <si>
+    <t>S/M TLK ANGIN BG 5'S</t>
+  </si>
+  <si>
+    <t>20064503</t>
+  </si>
+  <si>
+    <t>S/M TLK LINU HRB 5'S</t>
+  </si>
+  <si>
+    <t>20059240</t>
+  </si>
+  <si>
+    <t>ANTANGIN JUNIOR 5'S</t>
+  </si>
+  <si>
+    <t>20041621</t>
+  </si>
+  <si>
+    <t>ANTANGIN JRG 5X15ML</t>
+  </si>
+  <si>
+    <t>20114432</t>
+  </si>
+  <si>
+    <t>ANTANGIN HTBTSDA 5'S</t>
+  </si>
+  <si>
+    <t>20054969</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNGR/M 5X15</t>
+  </si>
+  <si>
+    <t>20143712</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNIGHT BOX</t>
+  </si>
+  <si>
+    <t>20093959</t>
+  </si>
+  <si>
+    <t>BEJO JAHE MERAH 6X15</t>
+  </si>
+  <si>
+    <t>20137415</t>
+  </si>
+  <si>
+    <t>MXGRP GRGES JLM 6S</t>
+  </si>
+  <si>
+    <t>20124231</t>
+  </si>
+  <si>
+    <t>MADU TJ MSK ANGIN140</t>
+  </si>
+  <si>
+    <t>20088783</t>
+  </si>
+  <si>
+    <t>MADU TJ PNS DLM 150</t>
+  </si>
+  <si>
+    <t>10003799</t>
+  </si>
+  <si>
+    <t>EXTRA JOSS BOX 6'S</t>
+  </si>
+  <si>
+    <t>20039339</t>
+  </si>
+  <si>
+    <t>SILADEX O/B EXP 60</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20143398</t>
+  </si>
+  <si>
+    <t>ACTF SYRUP PILEK 25</t>
+  </si>
+  <si>
+    <t>20138372</t>
+  </si>
+  <si>
+    <t>KOMIX OBH 6X7ML</t>
+  </si>
+  <si>
+    <t>20092712</t>
+  </si>
+  <si>
+    <t>KOMIX HERBAL 4X15ML</t>
+  </si>
+  <si>
+    <t>10008599</t>
+  </si>
+  <si>
+    <t>OBH/C ANAK STRW 60ML</t>
+  </si>
+  <si>
+    <t>10023206</t>
+  </si>
+  <si>
+    <t>TERMOREX PLUS 60 ML</t>
+  </si>
+  <si>
+    <t>10006565</t>
+  </si>
+  <si>
+    <t>TEMPRA T/PNS ANGR 60</t>
+  </si>
+  <si>
+    <t>10000548</t>
+  </si>
+  <si>
+    <t>CAP LANG NORIT (40)</t>
+  </si>
+  <si>
+    <t>10038823</t>
+  </si>
+  <si>
+    <t>COMBANTRIN JRK 10ML</t>
+  </si>
+  <si>
+    <t>20021454</t>
+  </si>
+  <si>
+    <t>MYLANTA MAAG MINT 50</t>
+  </si>
+  <si>
+    <t>20052643</t>
+  </si>
+  <si>
+    <t>PROMAG HRBAL BOX 6'S</t>
+  </si>
+  <si>
+    <t>20057840</t>
+  </si>
+  <si>
+    <t>POLYSILANE BTL 100</t>
+  </si>
+  <si>
+    <t>20021214</t>
+  </si>
+  <si>
+    <t>VGTA HERBAL ANGR 6'S</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20107145</t>
+  </si>
+  <si>
+    <t>DULCOLAX 10'S</t>
+  </si>
+  <si>
+    <t>20002523</t>
+  </si>
+  <si>
+    <t>ROHTO OBT MATA COL 7</t>
+  </si>
+  <si>
+    <t>20105059</t>
+  </si>
+  <si>
+    <t>ROHTO V-EXTRA 7ML</t>
+  </si>
+  <si>
+    <t>10000149</t>
+  </si>
+  <si>
+    <t>INSTO REG. 7.5 ML</t>
+  </si>
+  <si>
+    <t>10015684</t>
+  </si>
+  <si>
+    <t>INSTO FRY EYES 7.5</t>
+  </si>
+  <si>
+    <t>20122751</t>
+  </si>
+  <si>
+    <t>INSTO COOL 7.5ML</t>
+  </si>
+  <si>
+    <t>20017270</t>
+  </si>
+  <si>
+    <t>VICKS F44 ANK STRW54</t>
+  </si>
+  <si>
+    <t>20120782</t>
+  </si>
+  <si>
+    <t>VICKS JAHE MADU 56ML</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000144</t>
+  </si>
+  <si>
+    <t>VICKS F44 DWSA 54ML</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20128049</t>
+  </si>
+  <si>
+    <t>VICKS INHALER TWIN</t>
+  </si>
+  <si>
+    <t>10000159</t>
+  </si>
+  <si>
+    <t>VICKS INHALER</t>
+  </si>
+  <si>
+    <t>20137940</t>
+  </si>
+  <si>
+    <t>VICKS BABY BALM 20G</t>
+  </si>
+  <si>
+    <t>20034842</t>
+  </si>
+  <si>
+    <t>VICKS VAPORUB POT 25</t>
+  </si>
+  <si>
+    <t>10020195</t>
+  </si>
+  <si>
+    <t>VICKS VAPORUB 50G</t>
+  </si>
+  <si>
+    <t>20143018</t>
+  </si>
+  <si>
+    <t>VCKS VPRB EXSTRG 25G</t>
+  </si>
+  <si>
+    <t>10000289</t>
+  </si>
+  <si>
+    <t>OBH.C PLUS MNTHL 100</t>
+  </si>
+  <si>
+    <t>10037392</t>
+  </si>
+  <si>
+    <t>OBH.C BDHK MNTHL 100</t>
+  </si>
+  <si>
+    <t>20131299</t>
+  </si>
+  <si>
+    <t>OBH COMBI HERBAL60ML</t>
+  </si>
+  <si>
+    <t>10002978</t>
+  </si>
+  <si>
+    <t>LASERIN O/BATUK 110M</t>
+  </si>
+  <si>
+    <t>20006531</t>
+  </si>
+  <si>
+    <t>WOODS O/B LIQ EXP 60</t>
+  </si>
+  <si>
+    <t>20129489</t>
+  </si>
+  <si>
+    <t>WOODS O/B LIQ NTRL60</t>
+  </si>
+  <si>
+    <t>20124758</t>
+  </si>
+  <si>
+    <t>OB/HRBL HBTSAUDA 60</t>
+  </si>
+  <si>
+    <t>20011850</t>
+  </si>
+  <si>
+    <t>OB HERBAL OBT BTK 60</t>
+  </si>
+  <si>
+    <t>20139611</t>
+  </si>
+  <si>
+    <t>FCARE STRONG 15+5ML</t>
+  </si>
+  <si>
+    <t>20040719</t>
+  </si>
+  <si>
+    <t>FRESH/C MYK/A STRG10</t>
+  </si>
+  <si>
+    <t>20034536</t>
+  </si>
+  <si>
+    <t>FRESH/C MNYK ANGIN10</t>
+  </si>
+  <si>
+    <t>20037203</t>
+  </si>
+  <si>
+    <t>FRESH/C MYK ANG LV10</t>
+  </si>
+  <si>
+    <t>20131218</t>
+  </si>
+  <si>
+    <t>FRS.CR SMASH IN+R/ON</t>
+  </si>
+  <si>
+    <t>20139612</t>
+  </si>
+  <si>
+    <t>FCARE SMASH FRUITY</t>
+  </si>
+  <si>
+    <t>20141438</t>
+  </si>
+  <si>
+    <t>FCARE SMASH SAKURA</t>
+  </si>
+  <si>
+    <t>20135134</t>
+  </si>
+  <si>
+    <t>FRS.CR IN+R/ON MTCHA</t>
+  </si>
+  <si>
+    <t>20141439</t>
+  </si>
+  <si>
+    <t>FCARE VPBLM SAKURA</t>
+  </si>
+  <si>
+    <t>20139593</t>
+  </si>
+  <si>
+    <t>FCARE VPOBALM MATCHA</t>
+  </si>
+  <si>
+    <t>20045178</t>
+  </si>
+  <si>
+    <t>SAFE/C MNYK ANGIN 10</t>
+  </si>
+  <si>
+    <t>20102037</t>
+  </si>
+  <si>
+    <t>SAFE/C MYK AGN STR10</t>
+  </si>
+  <si>
+    <t>20134253</t>
+  </si>
+  <si>
+    <t>SO FRSH HOT 2X10ML</t>
+  </si>
+  <si>
+    <t>20134254</t>
+  </si>
+  <si>
+    <t>SO FRSH EUCLYP2X10ML</t>
+  </si>
+  <si>
+    <t>20141329</t>
+  </si>
+  <si>
+    <t>SO FRSH CTRUS 2X10ML</t>
+  </si>
+  <si>
+    <t>20091326</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S ECALYPT10</t>
+  </si>
+  <si>
+    <t>20122013</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S CITRUS 10</t>
+  </si>
+  <si>
+    <t>20141330</t>
+  </si>
+  <si>
+    <t>PLOSSA DUAL SRGHAEYO</t>
+  </si>
+  <si>
+    <t>10000097</t>
+  </si>
+  <si>
+    <t>C/KAPAK MNYK ANGIN10</t>
+  </si>
+  <si>
+    <t>20054022</t>
+  </si>
+  <si>
+    <t>TAWON 912 O/GSK 50ML</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>20019446</t>
@@ -208,463 +658,13 @@
     <t>C/LANG MINYAK GPU 60</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20054951</t>
-  </si>
-  <si>
-    <t>S/M TOLAK/A ANAK 5'S</t>
-  </si>
-  <si>
-    <t>20034577</t>
-  </si>
-  <si>
-    <t>S/M TLK.ANGN+MDU 5'S</t>
-  </si>
-  <si>
-    <t>20122907</t>
-  </si>
-  <si>
-    <t>S/M TLK.ANGN FLU 5'S</t>
-  </si>
-  <si>
-    <t>20064502</t>
-  </si>
-  <si>
-    <t>S/M TLK ANGIN BG 5'S</t>
-  </si>
-  <si>
-    <t>20064503</t>
-  </si>
-  <si>
-    <t>S/M TLK LINU HRB 5'S</t>
-  </si>
-  <si>
-    <t>20059240</t>
-  </si>
-  <si>
-    <t>ANTANGIN JUNIOR 5'S</t>
-  </si>
-  <si>
-    <t>20041621</t>
-  </si>
-  <si>
-    <t>ANTANGIN JRG 5X15ML</t>
-  </si>
-  <si>
-    <t>20114432</t>
-  </si>
-  <si>
-    <t>ANTANGIN HTBTSDA 5'S</t>
-  </si>
-  <si>
-    <t>20054969</t>
-  </si>
-  <si>
-    <t>ANTANGIN GNGR/M 5X15</t>
-  </si>
-  <si>
-    <t>20093959</t>
-  </si>
-  <si>
-    <t>BEJO JAHE MERAH 6X15</t>
-  </si>
-  <si>
-    <t>20137415</t>
-  </si>
-  <si>
-    <t>MXGRP GRGES JLM 6S</t>
-  </si>
-  <si>
-    <t>20124231</t>
-  </si>
-  <si>
-    <t>MADU TJ MSK ANGIN140</t>
-  </si>
-  <si>
-    <t>20088783</t>
-  </si>
-  <si>
-    <t>MADU TJ PNS DLM 150</t>
-  </si>
-  <si>
-    <t>10003799</t>
-  </si>
-  <si>
-    <t>EXTRA JOSS BOX 6'S</t>
-  </si>
-  <si>
-    <t>20139960</t>
-  </si>
-  <si>
-    <t>EJ SPORT ORANGE 2S</t>
-  </si>
-  <si>
-    <t>20039339</t>
-  </si>
-  <si>
-    <t>SILADEX O/B EXP 60</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20143398</t>
-  </si>
-  <si>
-    <t>ACTF SYRUP PILEK 25</t>
-  </si>
-  <si>
-    <t>20138372</t>
-  </si>
-  <si>
-    <t>KOMIX OBH 6X7ML</t>
-  </si>
-  <si>
-    <t>20092712</t>
-  </si>
-  <si>
-    <t>KOMIX HERBAL 4X15ML</t>
-  </si>
-  <si>
-    <t>10008599</t>
-  </si>
-  <si>
-    <t>OBH/C ANAK STRW 60ML</t>
-  </si>
-  <si>
-    <t>10023206</t>
-  </si>
-  <si>
-    <t>TERMOREX PLUS 60 ML</t>
-  </si>
-  <si>
-    <t>10006565</t>
-  </si>
-  <si>
-    <t>TEMPRA T/PNS ANGR 60</t>
-  </si>
-  <si>
-    <t>10000548</t>
-  </si>
-  <si>
-    <t>CAP LANG NORIT (40)</t>
-  </si>
-  <si>
-    <t>10038823</t>
-  </si>
-  <si>
-    <t>COMBANTRIN JRK 10ML</t>
-  </si>
-  <si>
-    <t>20021454</t>
-  </si>
-  <si>
-    <t>MYLANTA MAAG MINT 50</t>
-  </si>
-  <si>
-    <t>20052643</t>
-  </si>
-  <si>
-    <t>PROMAG HRBAL BOX 6'S</t>
-  </si>
-  <si>
-    <t>20057840</t>
-  </si>
-  <si>
-    <t>POLYSILANE BTL 100</t>
-  </si>
-  <si>
-    <t>20021214</t>
-  </si>
-  <si>
-    <t>VGTA HERBAL ANGR 6'S</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20107145</t>
-  </si>
-  <si>
-    <t>DULCOLAX 10'S</t>
-  </si>
-  <si>
-    <t>20002523</t>
-  </si>
-  <si>
-    <t>ROHTO OBT MATA COL 7</t>
-  </si>
-  <si>
-    <t>20105059</t>
-  </si>
-  <si>
-    <t>ROHTO V-EXTRA 7ML</t>
-  </si>
-  <si>
-    <t>10000149</t>
-  </si>
-  <si>
-    <t>INSTO REG. 7.5 ML</t>
-  </si>
-  <si>
-    <t>10015684</t>
-  </si>
-  <si>
-    <t>INSTO FRY EYES 7.5</t>
-  </si>
-  <si>
-    <t>20122751</t>
-  </si>
-  <si>
-    <t>INSTO COOL 7.5ML</t>
-  </si>
-  <si>
-    <t>20017270</t>
-  </si>
-  <si>
-    <t>VICKS F44 ANK STRW54</t>
-  </si>
-  <si>
-    <t>20120782</t>
-  </si>
-  <si>
-    <t>VICKS JAHE MADU 56ML</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000144</t>
-  </si>
-  <si>
-    <t>VICKS F44 DWSA 54ML</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20128049</t>
-  </si>
-  <si>
-    <t>VICKS INHALER TWIN</t>
-  </si>
-  <si>
-    <t>10000159</t>
-  </si>
-  <si>
-    <t>VICKS INHALER</t>
-  </si>
-  <si>
-    <t>20137940</t>
-  </si>
-  <si>
-    <t>VICKS BABY BALM 20G</t>
-  </si>
-  <si>
-    <t>20034842</t>
-  </si>
-  <si>
-    <t>VICKS VAPORUB POT 25</t>
-  </si>
-  <si>
-    <t>10020195</t>
-  </si>
-  <si>
-    <t>VICKS VAPORUB 50G</t>
-  </si>
-  <si>
-    <t>20143018</t>
-  </si>
-  <si>
-    <t>VCKS VPRB EXSTRG 25G</t>
-  </si>
-  <si>
-    <t>10000289</t>
-  </si>
-  <si>
-    <t>OBH.C PLUS MNTHL 100</t>
-  </si>
-  <si>
-    <t>10037392</t>
-  </si>
-  <si>
-    <t>OBH.C BDHK MNTHL 100</t>
-  </si>
-  <si>
-    <t>20131299</t>
-  </si>
-  <si>
-    <t>OBH COMBI HERBAL60ML</t>
-  </si>
-  <si>
-    <t>10002978</t>
-  </si>
-  <si>
-    <t>LASERIN O/BATUK 110M</t>
-  </si>
-  <si>
-    <t>20006531</t>
-  </si>
-  <si>
-    <t>WOODS O/B LIQ EXP 60</t>
-  </si>
-  <si>
-    <t>20129489</t>
-  </si>
-  <si>
-    <t>WOODS O/B LIQ NTRL60</t>
-  </si>
-  <si>
-    <t>20124758</t>
-  </si>
-  <si>
-    <t>OB/HRBL HBTSAUDA 60</t>
-  </si>
-  <si>
-    <t>20011850</t>
-  </si>
-  <si>
-    <t>OB HERBAL OBT BTK 60</t>
-  </si>
-  <si>
-    <t>20139611</t>
-  </si>
-  <si>
-    <t>FCARE STRONG 15+5ML</t>
-  </si>
-  <si>
-    <t>20040719</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK/A STRG10</t>
-  </si>
-  <si>
-    <t>20034536</t>
-  </si>
-  <si>
-    <t>FRESH/C MNYK ANGIN10</t>
-  </si>
-  <si>
-    <t>20037203</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK ANG LV10</t>
-  </si>
-  <si>
-    <t>20131218</t>
-  </si>
-  <si>
-    <t>FRS.CR SMASH IN+R/ON</t>
-  </si>
-  <si>
-    <t>20139612</t>
-  </si>
-  <si>
-    <t>FCARE SMASH FRUITY</t>
-  </si>
-  <si>
-    <t>20141438</t>
-  </si>
-  <si>
-    <t>FCARE SMASH SAKURA</t>
-  </si>
-  <si>
-    <t>20135134</t>
-  </si>
-  <si>
-    <t>FRS.CR IN+R/ON MTCHA</t>
-  </si>
-  <si>
-    <t>20141439</t>
-  </si>
-  <si>
-    <t>FCARE VPBLM SAKURA</t>
-  </si>
-  <si>
-    <t>20139593</t>
-  </si>
-  <si>
-    <t>FCARE VPOBALM MATCHA</t>
-  </si>
-  <si>
-    <t>20045178</t>
-  </si>
-  <si>
-    <t>SAFE/C MNYK ANGIN 10</t>
-  </si>
-  <si>
-    <t>20102037</t>
-  </si>
-  <si>
-    <t>SAFE/C MYK AGN STR10</t>
-  </si>
-  <si>
-    <t>20134253</t>
-  </si>
-  <si>
-    <t>SO FRSH HOT 2X10ML</t>
-  </si>
-  <si>
-    <t>20134254</t>
-  </si>
-  <si>
-    <t>SO FRSH EUCLYP2X10ML</t>
-  </si>
-  <si>
-    <t>20141329</t>
-  </si>
-  <si>
-    <t>SO FRSH CTRUS 2X10ML</t>
-  </si>
-  <si>
-    <t>20091326</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S ECALYPT10</t>
-  </si>
-  <si>
-    <t>20122013</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S CITRUS 10</t>
-  </si>
-  <si>
-    <t>20141330</t>
-  </si>
-  <si>
-    <t>PLOSSA DUAL SRGHAEYO</t>
-  </si>
-  <si>
-    <t>10000097</t>
-  </si>
-  <si>
-    <t>C/KAPAK MNYK ANGIN10</t>
-  </si>
-  <si>
-    <t>20054022</t>
-  </si>
-  <si>
-    <t>TAWON 912 O/GSK 50ML</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>10000553</t>
   </si>
   <si>
     <t>BETADINE SOLUTION 30</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20137313</t>
-  </si>
-  <si>
-    <t>HANSPLST ANTSP 40ML</t>
   </si>
   <si>
     <t>22</t>
@@ -1760,7 +1760,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1800,15 +1800,15 @@
         <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1817,10 +1817,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1840,7 +1840,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1860,7 +1860,7 @@
         <v>39</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1880,15 +1880,15 @@
         <v>42</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1897,10 +1897,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1920,15 +1920,15 @@
         <v>49</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1937,10 +1937,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1960,7 +1960,7 @@
         <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2020,7 +2020,7 @@
         <v>65</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2197,7 +2197,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2220,7 +2220,7 @@
         <v>36</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2260,7 +2260,7 @@
         <v>42</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2277,10 +2277,10 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2300,7 +2300,7 @@
         <v>49</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2317,10 +2317,10 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>29</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2497,7 +2497,7 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>20</v>
@@ -2560,7 +2560,7 @@
         <v>42</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2577,7 +2577,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>123</v>
@@ -2617,7 +2617,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>20</v>
@@ -2877,7 +2877,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>16</v>
@@ -2957,7 +2957,7 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>123</v>
@@ -2977,7 +2977,7 @@
         <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>12</v>
@@ -3217,7 +3217,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3297,7 +3297,7 @@
         <v>19</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>123</v>
@@ -3337,7 +3337,7 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>123</v>
@@ -3460,7 +3460,7 @@
         <v>215</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3480,7 +3480,7 @@
         <v>218</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3520,7 +3520,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3960,7 +3960,7 @@
         <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4060,7 +4060,7 @@
         <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4120,7 +4120,7 @@
         <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4140,7 +4140,7 @@
         <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4317,7 +4317,7 @@
         <v>23</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>20</v>
@@ -4337,7 +4337,7 @@
         <v>23</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>12</v>
@@ -4357,7 +4357,7 @@
         <v>23</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>16</v>
@@ -4377,7 +4377,7 @@
         <v>23</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4397,7 +4397,7 @@
         <v>23</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>20</v>
@@ -4637,7 +4637,7 @@
         <v>23</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>123</v>
@@ -4657,7 +4657,7 @@
         <v>23</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>12</v>
@@ -4717,7 +4717,7 @@
         <v>23</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>123</v>
@@ -4737,7 +4737,7 @@
         <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>12</v>
@@ -4820,7 +4820,7 @@
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,7 +4840,7 @@
         <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,7 +4860,7 @@
         <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4900,7 +4900,7 @@
         <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4920,7 +4920,7 @@
         <v>23</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4940,7 +4940,7 @@
         <v>26</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4960,7 +4960,7 @@
         <v>29</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4977,10 +4977,10 @@
         <v>26</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5040,7 +5040,7 @@
         <v>42</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,7 +5057,7 @@
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5237,7 +5237,7 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>20</v>
